--- a/artfynd/A 23677-2023 artfynd.xlsx
+++ b/artfynd/A 23677-2023 artfynd.xlsx
@@ -1352,7 +1352,7 @@
         <v>101300893</v>
       </c>
       <c r="B8" t="n">
-        <v>58608</v>
+        <v>58641</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 23677-2023 artfynd.xlsx
+++ b/artfynd/A 23677-2023 artfynd.xlsx
@@ -1352,7 +1352,7 @@
         <v>101300893</v>
       </c>
       <c r="B8" t="n">
-        <v>58641</v>
+        <v>58654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 23677-2023 artfynd.xlsx
+++ b/artfynd/A 23677-2023 artfynd.xlsx
@@ -1352,7 +1352,7 @@
         <v>101300893</v>
       </c>
       <c r="B8" t="n">
-        <v>58654</v>
+        <v>58656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 23677-2023 artfynd.xlsx
+++ b/artfynd/A 23677-2023 artfynd.xlsx
@@ -1352,7 +1352,7 @@
         <v>101300893</v>
       </c>
       <c r="B8" t="n">
-        <v>58656</v>
+        <v>58666</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 23677-2023 artfynd.xlsx
+++ b/artfynd/A 23677-2023 artfynd.xlsx
@@ -1352,7 +1352,7 @@
         <v>101300893</v>
       </c>
       <c r="B8" t="n">
-        <v>58666</v>
+        <v>58668</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 23677-2023 artfynd.xlsx
+++ b/artfynd/A 23677-2023 artfynd.xlsx
@@ -1352,7 +1352,7 @@
         <v>101300893</v>
       </c>
       <c r="B8" t="n">
-        <v>58668</v>
+        <v>58670</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
